--- a/data/external/FPL_Evidence_Claims_Research_Pull.xlsx
+++ b/data/external/FPL_Evidence_Claims_Research_Pull.xlsx
@@ -432,7 +432,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sources: 2026-09-01_pull1_injuries_setpieces.md, 2026-09-01_pull2_predictedxi.md</t>
+          <t>sources: 2026-09-01_pull1_injuries_setpieces.md, 2026-09-01_pull2_predictedxi.md, 2026-10-07_fffix_gw6_forwards.md</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7906,6 +7906,63 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>Durable role change, not one-off rotation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Charalampos Kostoulas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>won_starting_spot</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Brighton's centre-forward since Danny Welbeck's move to Chelsea</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fantasy Football Fix</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>specialist</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>FPL data: started GW2-5 (79/90/83/75 min) after a 26-min GW1 sub cameo; 2 starts in all of 2025-26.</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10101,7 +10158,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Callum Wilson</t>
+          <t>Harry Wilson</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -10154,7 +10211,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Callum Wilson</t>
+          <t>Harry Wilson</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -11381,6 +11438,206 @@
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Penalties</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Dominic Calvert-Lewin</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Fantasy Football Fix</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>specialist</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>OPINION</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Article: "potential penalty duties". Agrees with the 2026-09-01 pull.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Penalties</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Dominic Calvert-Lewin</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lukas Nmecha</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Premier League official site</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>FPL's set-piece order: Calvert-Lewin 1, Nmecha 2, Piroe 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Penalties</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Oli McBurnie</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fantasy Football Fix</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>specialist</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>OPINION</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Article: "potential penalty duties".</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Penalties</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Oli McBurnie</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Premier League official site</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>official</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>FACT</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>FPL's set-piece order lists McBurnie first and no second taker. The 2026-09-01 pull's Crooks-first row (fplcopilot) disagrees.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
